--- a/input.xlsx
+++ b/input.xlsx
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -752,12 +752,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -779,22 +779,73 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>U9</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Sandefjord</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>U9</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>U11</t>
         </is>

--- a/input.xlsx
+++ b/input.xlsx
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -848,6 +848,23 @@
       <c r="C8" t="inlineStr">
         <is>
           <t>U11</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>U12</t>
         </is>
       </c>
     </row>

--- a/input.xlsx
+++ b/input.xlsx
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -837,12 +837,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -854,15 +854,49 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Kongsberg/Tønsberg</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kongsberg/Tønsberg</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>JU12</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Kongsberg</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Kongsberg</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>U12</t>
         </is>

--- a/input.xlsx
+++ b/input.xlsx
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -735,12 +735,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -752,17 +752,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U7</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U7</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
@@ -830,73 +830,107 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Kongsberg/Tønsberg</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kongsberg/Tønsberg</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>JU12</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Kongsberg</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Kongsberg</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>U12</t>
         </is>

--- a/input.xlsx
+++ b/input.xlsx
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -769,12 +769,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -786,29 +786,29 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -820,29 +820,29 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -854,17 +854,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
@@ -881,19 +881,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -905,32 +905,49 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Kongsberg/Tønsberg</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kongsberg/Tønsberg</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>JU12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Kongsberg</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Kongsberg</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>U12</t>
         </is>

--- a/input.xlsx
+++ b/input.xlsx
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -803,12 +803,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -820,12 +820,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -837,34 +837,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
@@ -881,58 +881,58 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
@@ -948,6 +948,74 @@
         </is>
       </c>
       <c r="C14" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Kongsberg/Tønsberg</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kongsberg/Tønsberg</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>JU12</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>U12</t>
         </is>

--- a/input.xlsx
+++ b/input.xlsx
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -871,12 +871,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker 5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -888,12 +888,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -905,29 +905,29 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -939,89 +939,173 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>U9</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Kongsberg</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Kongsberg</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" collapsed="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Kongsberg/Tønsberg</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kongsberg/Tønsberg</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>JU12</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>U12</t>
         </is>
       </c>
     </row>
-    <row r="21" collapsed="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/input.xlsx
+++ b/input.xlsx
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -927,7 +927,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -990,12 +990,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker 5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1007,12 +1007,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1024,83 +1024,185 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="21" collapsed="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Frisk Asker 4</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Frisk Asker 5</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Kongsberg</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Kongsberg</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Kongsberg/Tønsberg</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Kongsberg/Tønsberg</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>JU12</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>U12</t>
         </is>

--- a/input.xlsx
+++ b/input.xlsx
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -769,12 +769,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -786,17 +786,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>U7</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -854,12 +854,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -871,12 +871,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Frisk Asker 5</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -888,34 +888,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Frisk Asker 5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -973,12 +973,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -990,12 +990,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Frisk Asker 5</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1007,34 +1007,34 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Frisk Asker 5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Frisk Asker 6</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1109,12 +1109,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Frisk Asker 5</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1126,29 +1126,29 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1160,12 +1160,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1177,32 +1177,66 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Kongsberg/Tønsberg</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Kongsberg/Tønsberg</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>JU12</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Kongsberg</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Kongsberg</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>U12</t>
         </is>

--- a/input.xlsx
+++ b/input.xlsx
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1228,15 +1228,83 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Frisk Asker 1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Frisk Asker 2</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Frisk Asker 3</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Frisk Asker 4</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>Kongsberg</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Kongsberg</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>U12</t>
         </is>

--- a/input.xlsx
+++ b/input.xlsx
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>JU8</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -854,12 +854,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -871,12 +871,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -888,17 +888,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Frisk Asker 5</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -973,12 +973,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker 5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -990,12 +990,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1007,17 +1007,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Frisk Asker Svart</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Frisk Asker 5</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Frisk Asker 6</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1109,12 +1109,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Frisk Asker 5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
@@ -1148,41 +1148,41 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Frisk Asker 6</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1194,12 +1194,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1211,68 +1211,68 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1296,15 +1296,66 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Frisk Asker 2</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Frisk Asker 3</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Frisk Asker 4</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>Kongsberg</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Kongsberg</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>U12</t>
         </is>

--- a/input.xlsx
+++ b/input.xlsx
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1262,12 +1262,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1284,29 +1284,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Frisk Asker Svart</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1347,15 +1347,49 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Frisk Asker 3</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Frisk Asker 4</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Kongsberg</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Kongsberg</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>U12</t>
         </is>

--- a/input.xlsx
+++ b/input.xlsx
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -786,17 +786,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>JU8</t>
+          <t>U7</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>JU8</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -871,12 +871,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -888,12 +888,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -905,34 +905,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Frisk Asker 5</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -990,12 +990,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1007,12 +1007,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Frisk Asker 5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1024,51 +1024,51 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="21" collapsed="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Frisk Asker Svart</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Frisk Asker 5</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Frisk Asker 6</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1160,12 +1160,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Frisk Asker 5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
@@ -1199,58 +1199,58 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Frisk Asker 6</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
@@ -1284,80 +1284,80 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Tønsberg Hvit</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Tønsberg Rød</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
@@ -1369,27 +1369,180 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Frisk Asker Svart</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>JU12</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Kongsberg/Tønsberg</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Kongsberg/Tønsberg</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>JU12</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Frisk Asker 1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Frisk Asker 2</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Frisk Asker 3</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Frisk Asker 4</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>Kongsberg</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>Kongsberg</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Tønsberg</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Tønsberg Grå</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Tønsberg</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Tønsberg Hvit</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Tønsberg</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Tønsberg Rød</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
         <is>
           <t>U12</t>
         </is>

--- a/input.xlsx
+++ b/input.xlsx
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C79"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -769,12 +769,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -786,12 +786,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jar Grønn</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -803,68 +803,68 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>JU8</t>
+          <t>U7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U7</t>
         </is>
       </c>
     </row>
@@ -876,41 +876,41 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>JU8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>JU8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -922,12 +922,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
@@ -961,131 +961,131 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Frisk Asker 5</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="21" collapsed="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
@@ -1165,114 +1165,114 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Frisk Asker 5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Frisk Asker 5</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Frisk Asker 6</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
@@ -1284,80 +1284,80 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker Svart</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tønsberg Hvit</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tønsberg Rød</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
@@ -1386,29 +1386,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Frisk Asker 5</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
@@ -1420,114 +1420,114 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Frisk Asker 6</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Jar Grønn</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tønsberg Grå</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tønsberg Hvit</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
@@ -1539,10 +1539,520 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>Tønsberg</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>U10</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Frisk Asker 1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Frisk Asker 2</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Frisk Asker 3</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Jar Blå</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Jar Grønn</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Jar Gul</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Jar Hvit</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Jar Oransje</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Jar Rød</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Jar Svart</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Tønsberg</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Tønsberg Hvit</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Tønsberg</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
           <t>Tønsberg Rød</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Frisk Asker Orange</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>JU12</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Frisk Asker Svart</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>JU12</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Jar Hvit</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>JU12</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Kongsberg/Tønsberg</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Kongsberg/Tønsberg</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>JU12</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Frisk Asker 1</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Frisk Asker 2</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Frisk Asker 3</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Frisk Asker 4</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Jar Blå</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Jar Hvit</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Jar Lilla</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Jar Rød</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Tønsberg</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Tønsberg Grå</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Tønsberg</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Tønsberg Hvit</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Tønsberg</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Tønsberg Rød</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
         <is>
           <t>U12</t>
         </is>

--- a/input.xlsx
+++ b/input.xlsx
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C79"/>
+  <dimension ref="A1:C97"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -905,34 +905,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>JU8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>JU8</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -973,12 +973,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -990,12 +990,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1058,12 +1058,12 @@
     <row r="21" collapsed="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1075,12 +1075,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1092,68 +1092,68 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Frisk Asker 5</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1177,12 +1177,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1194,12 +1194,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1211,12 +1211,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1228,12 +1228,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker 5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1245,12 +1245,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1262,12 +1262,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1279,85 +1279,85 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
@@ -1386,75 +1386,75 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Frisk Asker Svart</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Frisk Asker 5</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Frisk Asker 6</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Jar Grønn</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1466,12 +1466,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1483,12 +1483,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1500,12 +1500,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1517,12 +1517,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker 5</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1534,12 +1534,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Frisk Asker 6</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1551,51 +1551,51 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Jar Grønn</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
@@ -1624,109 +1624,109 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Jar Grønn</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Jar Gul</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Jar Oransje</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Ringerike 3</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1738,12 +1738,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tønsberg Hvit</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1772,12 +1772,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tønsberg Rød</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1789,34 +1789,34 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Jar Grønn</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Jar Gul</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
@@ -1833,226 +1833,532 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Jar Oransje</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Jar Lilla</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Tønsberg Hvit</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Tønsberg Rød</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tønsberg Grå</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Tønsberg Hvit</t>
+          <t>Frisk Asker Svart</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Jar Hvit</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>JU12</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Kongsberg/Tønsberg</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Kongsberg/Tønsberg</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>JU12</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Ringerike</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Ringerike 1</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>JU12</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Ringerike</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Ringerike 2</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>JU12</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Skien</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Skien</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>JU12</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Frisk Asker 1</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Frisk Asker 2</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Frisk Asker 3</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Frisk Asker 4</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Jar Blå</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Jar Hvit</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Jar Lilla</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Jar Rød</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Ringerike</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Ringerike 1</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Ringerike</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Ringerike 2</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
           <t>Tønsberg</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Tønsberg Grå</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Tønsberg</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Tønsberg Hvit</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Tønsberg</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
         <is>
           <t>Tønsberg Rød</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>U12</t>
         </is>

--- a/input.xlsx
+++ b/input.xlsx
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C97"/>
+  <dimension ref="A1:C99"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1143,12 +1143,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1160,17 +1160,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Frisk Asker 5</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1245,12 +1245,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Frisk Asker 5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1296,12 +1296,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1313,12 +1313,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1330,12 +1330,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1347,12 +1347,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1364,46 +1364,46 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1415,12 +1415,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Frisk Asker Svart</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1432,12 +1432,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1449,34 +1449,34 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Frisk Asker 5</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Frisk Asker 6</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1551,12 +1551,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Frisk Asker 5</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1568,12 +1568,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Jar Grønn</t>
+          <t>Frisk Asker 6</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Jar Grønn</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1636,12 +1636,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1653,12 +1653,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1670,12 +1670,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ringerike 3</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1704,12 +1704,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1721,34 +1721,34 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Ringerike 3</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1772,12 +1772,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1789,12 +1789,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Jar Grønn</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Jar Gul</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Jar Grønn</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Jar Oransje</t>
+          <t>Jar Gul</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Jar Oransje</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1891,12 +1891,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1908,12 +1908,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1925,12 +1925,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1942,12 +1942,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1959,12 +1959,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1976,12 +1976,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tønsberg Hvit</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1993,12 +1993,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tønsberg Rød</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2010,46 +2010,46 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Tønsberg Hvit</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Tønsberg Rød</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2061,12 +2061,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Frisk Asker Svart</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2078,12 +2078,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2095,12 +2095,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2112,12 +2112,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2129,34 +2129,34 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2197,12 +2197,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2214,12 +2214,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Jar Lilla</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2265,12 +2265,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar Lilla</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2282,12 +2282,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2299,12 +2299,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2316,12 +2316,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Tønsberg Grå</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2333,12 +2333,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Tønsberg Hvit</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2355,10 +2355,44 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
+          <t>Tønsberg Grå</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Tønsberg</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Tønsberg Hvit</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Tønsberg</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
           <t>Tønsberg Rød</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>U12</t>
         </is>

--- a/input.xlsx
+++ b/input.xlsx
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C99"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -837,12 +837,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -854,12 +854,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -871,46 +871,46 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>JU8</t>
+          <t>U7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>JU8</t>
+          <t>U7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -922,12 +922,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -939,34 +939,34 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>JU8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>JU8</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1007,12 +1007,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1024,12 +1024,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1075,12 +1075,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1092,12 +1092,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1109,12 +1109,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1126,12 +1126,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1160,12 +1160,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1177,34 +1177,34 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Frisk Asker 5</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1262,12 +1262,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1279,12 +1279,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Frisk Asker 5</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1313,12 +1313,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1330,12 +1330,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1347,12 +1347,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1364,12 +1364,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1381,12 +1381,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1398,46 +1398,46 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1449,12 +1449,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Frisk Asker Svart</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1466,12 +1466,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1483,34 +1483,34 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Frisk Asker 5</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Frisk Asker 6</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1585,12 +1585,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Frisk Asker 5</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1602,12 +1602,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Jar Grønn</t>
+          <t>Frisk Asker 6</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Jar Grønn</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1670,12 +1670,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1687,12 +1687,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1704,12 +1704,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ringerike 3</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1738,12 +1738,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1755,34 +1755,34 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Ringerike 3</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1806,12 +1806,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1823,12 +1823,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Jar Grønn</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Jar Gul</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Jar Grønn</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Jar Oransje</t>
+          <t>Jar Gul</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Jar Oransje</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1925,12 +1925,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1942,12 +1942,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1959,12 +1959,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1976,12 +1976,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1993,12 +1993,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2010,12 +2010,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tønsberg Hvit</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2027,12 +2027,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Tønsberg Rød</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2044,46 +2044,46 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Tønsberg Hvit</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Tønsberg Rød</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2095,12 +2095,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Frisk Asker Svart</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2112,12 +2112,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2129,12 +2129,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2146,12 +2146,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2163,34 +2163,34 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2231,12 +2231,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2248,12 +2248,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Jar Lilla</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2299,12 +2299,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar Lilla</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2316,12 +2316,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2333,12 +2333,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2350,12 +2350,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Tønsberg Grå</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2367,12 +2367,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Tønsberg Hvit</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2389,10 +2389,44 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
+          <t>Tønsberg Grå</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Tønsberg</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Tønsberg Hvit</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Tønsberg</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
           <t>Tønsberg Rød</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>U12</t>
         </is>

--- a/input.xlsx
+++ b/input.xlsx
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C116"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -939,12 +939,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -956,12 +956,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -973,17 +973,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>JU8</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1109,12 +1109,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1126,12 +1126,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Jutul Hvit</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1160,12 +1160,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1177,12 +1177,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1194,12 +1194,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1211,68 +1211,68 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Frisk Asker 5</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1296,12 +1296,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1313,12 +1313,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1330,12 +1330,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1347,12 +1347,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker 5</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1364,12 +1364,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1381,12 +1381,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1398,12 +1398,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1415,12 +1415,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1432,51 +1432,51 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Jutul Gul</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
@@ -1493,58 +1493,58 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
@@ -1573,75 +1573,75 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Frisk Asker Svart</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Frisk Asker 5</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Frisk Asker 6</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Jar Grønn</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1653,12 +1653,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1670,12 +1670,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1687,12 +1687,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1704,12 +1704,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker 5</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1721,12 +1721,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Frisk Asker 6</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1738,12 +1738,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ringerike 3</t>
+          <t>Jar Grønn</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1772,12 +1772,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1789,182 +1789,182 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Jutul Hvit</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Jar Grønn</t>
+          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Jar Gul</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Jar Oransje</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Ringerike 3</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1976,12 +1976,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1993,12 +1993,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2010,12 +2010,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2027,12 +2027,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar Grønn</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2044,12 +2044,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Tønsberg Hvit</t>
+          <t>Jar Gul</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2061,12 +2061,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tønsberg Rød</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2078,34 +2078,34 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Jar Oransje</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
@@ -2117,199 +2117,199 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Jutul Hvit</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Tønsberg Hvit</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Tønsberg Rød</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Jar Lilla</t>
+          <t>Frisk Asker Svart</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
     </row>
@@ -2321,46 +2321,46 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jutul Kittens</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
     </row>
@@ -2372,61 +2372,316 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Tønsberg Grå</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Tønsberg Hvit</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Frisk Asker 1</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Frisk Asker 2</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Frisk Asker 3</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Frisk Asker 4</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Jar Blå</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Jar Hvit</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Jar Lilla</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Jar Rød</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Jutul</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Jutul Grønn</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Jutul</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Jutul Rød</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Ringerike</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Ringerike 1</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Ringerike</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Ringerike 2</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
           <t>Tønsberg</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Tønsberg Grå</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Tønsberg</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Tønsberg Hvit</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Tønsberg</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
         <is>
           <t>Tønsberg Rød</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C116" t="inlineStr">
         <is>
           <t>U12</t>
         </is>

--- a/input.xlsx
+++ b/input.xlsx
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C116"/>
+  <dimension ref="A1:C117"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1942,12 +1942,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Ringerike 4</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1959,17 +1959,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2010,12 +2010,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Jar Grønn</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Jar Gul</t>
+          <t>Jar Grønn</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Jar Gul</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Jar Oransje</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Jar Oransje</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2129,12 +2129,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Jutul Hvit</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Jutul Rød</t>
+          <t>Jutul Hvit</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2163,12 +2163,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2180,12 +2180,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2214,12 +2214,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2231,12 +2231,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2248,12 +2248,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Tønsberg Hvit</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Tønsberg Rød</t>
+          <t>Tønsberg Hvit</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2282,17 +2282,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Tønsberg Rød</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2316,12 +2316,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Frisk Asker Svart</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2333,12 +2333,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Jutul Kittens</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2350,12 +2350,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Jutul Kittens</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2367,12 +2367,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2401,12 +2401,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2418,17 +2418,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>JU12</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2486,12 +2486,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Jar Lilla</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Jar Lilla</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2554,12 +2554,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Jutul Rød</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2588,12 +2588,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2605,12 +2605,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2639,12 +2639,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Tønsberg Grå</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Tønsberg Hvit</t>
+          <t>Tønsberg Grå</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2678,10 +2678,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
+          <t>Tønsberg Hvit</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Tønsberg</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
           <t>Tønsberg Rød</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="C117" t="inlineStr">
         <is>
           <t>U12</t>
         </is>

--- a/input.xlsx
+++ b/input.xlsx
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C117"/>
+  <dimension ref="A1:C155"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -769,12 +769,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -786,12 +786,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jar Grønn</t>
+          <t>Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -803,12 +803,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -820,12 +820,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Holmen Hockey Sort</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -837,12 +837,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -854,12 +854,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jutul Rød</t>
+          <t>Jar Grønn</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -871,12 +871,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -888,12 +888,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -905,34 +905,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>JU8</t>
+          <t>U7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>JU8</t>
+          <t>U7</t>
         </is>
       </c>
     </row>
@@ -944,63 +944,63 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Jutul Hvit</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>JU8</t>
+          <t>U7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>JU8</t>
+          <t>U7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>JU8</t>
+          <t>U7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U7</t>
         </is>
       </c>
     </row>
@@ -1012,126 +1012,126 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>JU8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>JU8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>JU8</t>
         </is>
       </c>
     </row>
     <row r="21" collapsed="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>JU8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Jutul Kittens</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>JU8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>JU8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>JU8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Jutul Hvit</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1160,12 +1160,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jutul Rød</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1177,12 +1177,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1194,12 +1194,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Frisk Asker 5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1211,12 +1211,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Holmen Hockey Blå</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1228,12 +1228,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1245,12 +1245,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1262,12 +1262,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Holmen Hockey Sort</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1279,250 +1279,250 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Frisk Asker 5</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Jutul Gul</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Jutul Hvit</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Jutul Gul</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Jutul Rød</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1534,12 +1534,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
@@ -1573,420 +1573,420 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Frisk Asker 5</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Holmen Hockey Sort</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Frisk Asker 5</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Frisk Asker 6</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Jutul Gul</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Jar Grønn</t>
+          <t>Jutul Hvit</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Jutul Hvit</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Jutul Rød</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Frisk Asker Svart</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ringerike 3</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ringerike 4</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
@@ -2015,369 +2015,369 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Jar Grønn</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Jar Gul</t>
+          <t>Frisk Asker 5</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Frisk Asker 6</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Jar Oransje</t>
+          <t>Holmen Hockey Blå</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Jutul Hvit</t>
+          <t>Holmen Hockey Sort</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Jutul Rød</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar Grønn</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Jar Gul</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Tønsberg Hvit</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Tønsberg Rød</t>
+          <t>Jutul Hvit</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Jutul Kittens</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Ringerike 3</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
@@ -2389,46 +2389,46 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Ringerike 4</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
@@ -2457,12 +2457,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
@@ -2474,46 +2474,46 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
@@ -2525,12 +2525,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Jar Lilla</t>
+          <t>Jar Grønn</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
@@ -2559,146 +2559,792 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Jar Gul</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Jutul Rød</t>
+          <t>Jar Lilla</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Jar Oransje</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Tønsberg Grå</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Tønsberg Hvit</t>
+          <t>Jutul Hvit</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>U12</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
+          <t>Jutul</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Jutul Rød</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Ringerike</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Ringerike 1</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Ringerike</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Ringerike 2</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Skien</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Skien</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
           <t>Tønsberg</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Tønsberg Grå</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Tønsberg</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Tønsberg Hvit</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Tønsberg</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
         <is>
           <t>Tønsberg Rød</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>U11</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Frisk Asker Orange</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>JU12</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Frisk Asker Svart</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>JU12</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>JU12</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Jar Hvit</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>JU12</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Jutul</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Jutul Kittens</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>JU12</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Jutul</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Jutul/Jar Kittens</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>JU12</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Kongsberg/Tønsberg</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Kongsberg/Tønsberg</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>JU12</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Ringerike</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Ringerike 1</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>JU12</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Ringerike</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Ringerike 2</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>JU12</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Skien</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Skien</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>JU12</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Tønsberg</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Tønsberg</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>JU12</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Frisk Asker 1</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Frisk Asker 2</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Frisk Asker 3</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Frisk Asker</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Frisk Asker 4</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Holmen Hockey Hvit</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Holmen Hockey Rød</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Jar Blå</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Jar Hvit</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Jar Lilla</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Jar Rød</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Jar</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Jar Svart</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Jutul</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Jutul Grønn</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Jutul</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Jutul Rød</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Kongsberg</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Ringerike</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Ringerike 1</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Ringerike</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Ringerike 2</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Tønsberg</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Tønsberg Grå</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Tønsberg</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Tønsberg Hvit</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>U12</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Tønsberg</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Tønsberg Rød</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
         <is>
           <t>U12</t>
         </is>

--- a/input.xlsx
+++ b/input.xlsx
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C155"/>
+  <dimension ref="A1:C146"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1041,12 +1041,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Jutul Kittens</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1058,12 +1058,12 @@
     <row r="21" collapsed="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1075,12 +1075,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jutul Kittens</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1092,34 +1092,34 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>JU8</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>JU8</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Frisk Asker 5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1177,12 +1177,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Holmen Hockey Blå</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1194,12 +1194,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Frisk Asker 5</t>
+          <t>Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Holmen Hockey Blå</t>
+          <t>Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit</t>
+          <t>Holmen Hockey Sort</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1245,12 +1245,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1262,12 +1262,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Holmen Hockey Sort</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1313,12 +1313,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1330,12 +1330,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Jutul Gul</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Jutul Hvit</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Jutul Gul</t>
+          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1381,12 +1381,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Jutul Hvit</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1398,12 +1398,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Jutul Rød</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1415,12 +1415,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1432,12 +1432,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1449,12 +1449,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1466,12 +1466,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1483,34 +1483,34 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1551,12 +1551,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1568,12 +1568,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1585,12 +1585,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Frisk Asker 5</t>
+          <t>Holmen Hockey Sort</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1602,12 +1602,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1619,12 +1619,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1636,12 +1636,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Holmen Hockey Sort</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1653,12 +1653,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1670,12 +1670,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Jutul Hvit</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1687,12 +1687,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1704,12 +1704,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1721,12 +1721,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1738,12 +1738,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Jutul Gul</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Jutul Hvit</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1772,12 +1772,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Jutul Rød</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1789,97 +1789,97 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Frisk Asker Svart</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1891,12 +1891,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1908,85 +1908,85 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Frisk Asker 5</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Frisk Asker 6</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2010,12 +2010,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Holmen Hockey Blå</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2027,12 +2027,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2044,12 +2044,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2061,12 +2061,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Frisk Asker 5</t>
+          <t>Holmen Hockey Sort</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2078,12 +2078,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Frisk Asker 6</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2095,12 +2095,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Holmen Hockey Blå</t>
+          <t>Jar Grønn</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2112,12 +2112,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit</t>
+          <t>Jar Gul</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2129,12 +2129,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2146,12 +2146,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Holmen Hockey Sort</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2180,12 +2180,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Jar Grønn</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2197,12 +2197,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Jar Gul</t>
+          <t>Jutul Hvit</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2214,12 +2214,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2231,12 +2231,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2248,12 +2248,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2265,12 +2265,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2282,12 +2282,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Jutul Hvit</t>
+          <t>Ringerike 3</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2299,12 +2299,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Jutul Rød</t>
+          <t>Ringerike 4</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2316,12 +2316,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2333,97 +2333,97 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ringerike 3</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Ringerike 4</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2435,12 +2435,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2452,12 +2452,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Jar Grønn</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2469,12 +2469,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Jar Gul</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2486,12 +2486,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2503,12 +2503,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød</t>
+          <t>Jar Lilla</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Jar Oransje</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Jar Grønn</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Jar Gul</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2571,12 +2571,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2588,12 +2588,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Jar Lilla</t>
+          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2605,12 +2605,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Jar Oransje</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2622,12 +2622,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2639,12 +2639,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -2656,12 +2656,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2673,12 +2673,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Jutul Hvit</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -2690,12 +2690,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Jutul Rød</t>
+          <t>Tønsberg Grå</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2707,12 +2707,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Tønsberg Hvit</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -2724,12 +2724,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Tønsberg Rød</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -2741,114 +2741,114 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>JU12</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Frisk Asker Svart</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>JU12</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>JU12</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Tønsberg Grå</t>
+          <t>Jutul/Jar Kittens</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>JU12</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Tønsberg Hvit</t>
+          <t>Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>JU12</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Tønsberg Rød</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>JU12</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -2860,12 +2860,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -2877,12 +2877,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -2894,148 +2894,148 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Jutul Kittens</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Jutul/Jar Kittens</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3047,12 +3047,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3064,12 +3064,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3081,12 +3081,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3098,12 +3098,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3115,12 +3115,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3132,12 +3132,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3149,12 +3149,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Tønsberg Grå</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3166,12 +3166,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Jar Lilla</t>
+          <t>Tønsberg Hvit</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -3183,168 +3183,15 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Tønsberg Rød</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
-        <is>
-          <t>U12</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Jar</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Jar Svart</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>U12</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Jutul</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Jutul Grønn</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>U12</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Jutul</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Jutul Rød</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>U12</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Kongsberg</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Kongsberg</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>U12</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Ringerike</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Ringerike 1</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>U12</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Ringerike</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Ringerike 2</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>U12</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Tønsberg</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Tønsberg Grå</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>U12</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Tønsberg</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Tønsberg Hvit</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>U12</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Tønsberg</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Tønsberg Rød</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
         <is>
           <t>U12</t>
         </is>

--- a/input.xlsx
+++ b/input.xlsx
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C146"/>
+  <dimension ref="A1:C145"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2775,12 +2775,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul/Jar Kittens</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -2792,12 +2792,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Jutul/Jar Kittens</t>
+          <t>Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -2809,12 +2809,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -2843,12 +2843,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -2860,12 +2860,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -2877,17 +2877,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -2945,12 +2945,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit</t>
+          <t>Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -2979,12 +2979,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3047,12 +3047,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3081,12 +3081,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Jutul Rød</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3098,12 +3098,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3132,12 +3132,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Tønsberg Grå</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Tønsberg Grå</t>
+          <t>Tønsberg Hvit</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3171,27 +3171,10 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Tønsberg Hvit</t>
+          <t>Tønsberg Rød</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
-        <is>
-          <t>U12</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Tønsberg</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Tønsberg Rød</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
         <is>
           <t>U12</t>
         </is>

--- a/input.xlsx
+++ b/input.xlsx
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C145"/>
+  <dimension ref="A1:C144"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2928,12 +2928,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit</t>
+          <t>Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -2962,12 +2962,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3030,12 +3030,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3064,12 +3064,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Jutul Rød</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3081,12 +3081,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3115,12 +3115,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Tønsberg Grå</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Tønsberg Grå</t>
+          <t>Tønsberg Hvit</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3154,27 +3154,10 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Tønsberg Hvit</t>
+          <t>Tønsberg Rød</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
-        <is>
-          <t>U12</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Tønsberg</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Tønsberg Rød</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
         <is>
           <t>U12</t>
         </is>

--- a/input.xlsx
+++ b/input.xlsx
@@ -533,7 +533,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
@@ -552,7 +552,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
@@ -571,7 +571,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -590,7 +590,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -609,7 +609,7 @@
         <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
         <v>4</v>
@@ -628,7 +628,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
         <v>4</v>
@@ -647,7 +647,7 @@
         <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
@@ -666,7 +666,7 @@
         <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="D9" t="n">
         <v>5</v>
@@ -685,7 +685,7 @@
         <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="D10" t="n">
         <v>5</v>
@@ -973,7 +973,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Sandefjord Penguins</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,7 +1466,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Sandefjord Penguins</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1823,7 +1823,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Sandefjord Penguins</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2758,7 +2758,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins Ishockeyklubb</t>
+          <t>Sandefjord Penguins</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3525,12 +3525,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sandefjord Penguins</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>outlook</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.bookup.no/Utleie/#Bug%C3%A5rdshallen___/view:item/id:4497/part:/place:3907:SANDEFJORD/q:sandefjord/r:31/mod:book</t>
         </is>
       </c>
     </row>

--- a/input.xlsx
+++ b/input.xlsx
@@ -3518,7 +3518,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.bookup.no/utleie/Index/860</t>
+          <t>https://www.bookup.no/utleie/Index/860#___/view:item/id:860/part:/r:8/mod:book</t>
         </is>
       </c>
     </row>

--- a/input.xlsx
+++ b/input.xlsx
@@ -3530,12 +3530,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>outlook</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://www.bookup.no/Utleie/#Bug%C3%A5rdshallen___/view:item/id:4497/part:/place:3907:SANDEFJORD/q:sandefjord/r:31/mod:book</t>
+          <t>fixed_allocation</t>
         </is>
       </c>
     </row>

--- a/input.xlsx
+++ b/input.xlsx
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C155"/>
+  <dimension ref="A1:C144"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="9.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -973,7 +973,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Jutul Kittens</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1058,12 +1058,12 @@
     <row r="21" collapsed="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1075,12 +1075,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jutul Kittens</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1092,34 +1092,34 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>JU8</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>JU8</t>
+          <t>U8</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Frisk Asker 5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1177,12 +1177,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Holmen Hockey Blå</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1194,12 +1194,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Frisk Asker 5</t>
+          <t>Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Holmen Hockey Blå</t>
+          <t>Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit</t>
+          <t>Holmen Hockey Sort</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1245,12 +1245,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1262,12 +1262,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Holmen Hockey Sort</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1313,12 +1313,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1330,12 +1330,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Jutul Gul</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Jutul Hvit</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Jutul Gul</t>
+          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1381,12 +1381,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Jutul Hvit</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1398,12 +1398,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Jutul Rød</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1415,12 +1415,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1432,12 +1432,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1449,12 +1449,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1466,12 +1466,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1483,34 +1483,34 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>U8</t>
+          <t>U9</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1551,12 +1551,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1568,12 +1568,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1585,12 +1585,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Frisk Asker 5</t>
+          <t>Holmen Hockey Sort</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1602,12 +1602,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1619,12 +1619,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1636,12 +1636,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Holmen Hockey Sort</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1653,12 +1653,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1670,12 +1670,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Jutul Hvit</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1687,12 +1687,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1704,12 +1704,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1721,12 +1721,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1738,12 +1738,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Jutul Gul</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Jutul Hvit</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1772,12 +1772,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Jutul Rød</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1789,97 +1789,97 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Frisk Asker Svart</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>JU10</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1891,12 +1891,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1908,85 +1908,85 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Frisk Asker 5</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>JU10</t>
+          <t>U10</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Frisk Asker 6</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2010,12 +2010,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Holmen Hockey Blå</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2027,12 +2027,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2044,12 +2044,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2061,12 +2061,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Frisk Asker 5</t>
+          <t>Holmen Hockey Sort</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2078,12 +2078,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Frisk Asker 6</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2095,12 +2095,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Holmen Hockey Blå</t>
+          <t>Jar Grønn</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2112,12 +2112,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit</t>
+          <t>Jar Gul</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2129,12 +2129,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2146,12 +2146,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Holmen Hockey Sort</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2180,12 +2180,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Jar Grønn</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2197,12 +2197,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Jar Gul</t>
+          <t>Jutul Hvit</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2214,12 +2214,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2231,12 +2231,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2248,12 +2248,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2265,12 +2265,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2282,12 +2282,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Jutul Hvit</t>
+          <t>Ringerike 3</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2299,12 +2299,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Jutul Rød</t>
+          <t>Ringerike 4</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2316,12 +2316,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2333,97 +2333,97 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ringerike 3</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Ringerike 4</t>
+          <t>Frisk Asker 4</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>U10</t>
+          <t>U11</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2435,12 +2435,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2452,12 +2452,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Jar Grønn</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2469,12 +2469,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Jar Gul</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2486,12 +2486,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2503,12 +2503,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød</t>
+          <t>Jar Lilla</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Jar Oransje</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Jar Grønn</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Jar Gul</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2571,12 +2571,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2588,12 +2588,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Jar Lilla</t>
+          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2605,12 +2605,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Jar Oransje</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2622,12 +2622,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Jar Rød</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2639,12 +2639,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Jar Svart</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -2656,12 +2656,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Sandefjord Penguins Ishockeyklubb</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Jutul Grønn</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2673,12 +2673,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Jutul Hvit</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -2690,12 +2690,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Jutul Rød</t>
+          <t>Tønsberg Grå</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2707,12 +2707,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Kongsberg</t>
+          <t>Tønsberg Hvit</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -2724,12 +2724,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Tønsberg Rød</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -2741,114 +2741,114 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Frisk Asker Orange</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>JU12</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Sandefjord Penguins</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Frisk Asker Svart</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>JU12</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jutul/Jar Kittens</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>JU12</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Tønsberg Grå</t>
+          <t>Kongsberg/Tønsberg</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>JU12</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Tønsberg Hvit</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>JU12</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Tønsberg Rød</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>JU12</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Frisk Asker Orange</t>
+          <t>Skien</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -2860,12 +2860,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Frisk Asker Svart</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -2877,165 +2877,165 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker 1</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Frisk Asker 2</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Frisk Asker</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Jutul Kittens</t>
+          <t>Frisk Asker 3</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Jutul</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Jutul/Jar Kittens</t>
+          <t>Holmen Hockey Hvit</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Kongsberg/Tønsberg</t>
+          <t>Holmen Hockey Rød</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Ringerike 1</t>
+          <t>Jar Blå</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Ringerike</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Ringerike 2</t>
+          <t>Jar Hvit</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Skien</t>
+          <t>Jar Rød</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jar</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Tønsberg</t>
+          <t>Jar Svart</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>JU12</t>
+          <t>U12</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Frisk Asker 1</t>
+          <t>Jutul Grønn</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3047,12 +3047,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Jutul</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Frisk Asker 2</t>
+          <t>Jutul Rød</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3064,12 +3064,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Frisk Asker 3</t>
+          <t>Kongsberg</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3081,12 +3081,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Frisk Asker</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Frisk Asker 4</t>
+          <t>Ringerike 1</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3098,12 +3098,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Ringerike</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Holmen Hockey Hvit</t>
+          <t>Ringerike 2</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3115,12 +3115,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Holmen</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Holmen Hockey Rød</t>
+          <t>Tønsberg Grå</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3132,12 +3132,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Jar Blå</t>
+          <t>Tønsberg Hvit</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3149,202 +3149,15 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Tønsberg</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Jar Hvit</t>
+          <t>Tønsberg Rød</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
-        <is>
-          <t>U12</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Jar</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Jar Lilla</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>U12</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Jar</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Jar Rød</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>U12</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Jar</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Jar Svart</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>U12</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Jutul</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Jutul Grønn</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>U12</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Jutul</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Jutul Rød</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>U12</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Kongsberg</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Kongsberg</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>U12</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Ringerike</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Ringerike 1</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>U12</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Ringerike</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Ringerike 2</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>U12</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Tønsberg</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Tønsberg Grå</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>U12</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Tønsberg</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Tønsberg Hvit</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>U12</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Tønsberg</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Tønsberg Rød</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
         <is>
           <t>U12</t>
         </is>

--- a/input.xlsx
+++ b/input.xlsx
@@ -455,7 +455,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2027-04-30</t>
+          <t>2027-03-28</t>
         </is>
       </c>
     </row>

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/niclasl/src/hockey/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{475FC319-29E6-F44C-9BE1-D111E45CCF9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{477B0544-71F0-5E4E-A657-DD1781C004EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38720" yWindow="-1640" windowWidth="26240" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38720" yWindow="-1640" windowWidth="26240" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Innstillinger" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="81">
   <si>
     <t>felt</t>
   </si>
@@ -41,9 +41,6 @@
   </si>
   <si>
     <t>2027-03-28</t>
-  </si>
-  <si>
-    <t>max_hosting_days_per_month</t>
   </si>
   <si>
     <t>age_group</t>
@@ -609,7 +606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.1640625" bestFit="1" customWidth="1"/>
@@ -640,16 +637,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -664,24 +654,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
         <v>7</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>10</v>
-      </c>
-      <c r="E1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>4</v>
@@ -698,7 +688,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>4</v>
@@ -715,7 +705,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <v>4</v>
@@ -732,7 +722,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -749,7 +739,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>3</v>
@@ -766,7 +756,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7">
         <v>3</v>
@@ -783,7 +773,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8">
         <v>3</v>
@@ -800,7 +790,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -817,7 +807,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10">
         <v>2</v>
@@ -851,1575 +841,1575 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" t="s">
-        <v>22</v>
-      </c>
       <c r="C1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
         <v>23</v>
       </c>
-      <c r="B2" t="s">
-        <v>24</v>
-      </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
         <v>27</v>
       </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s">
         <v>31</v>
       </c>
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" t="s">
         <v>37</v>
       </c>
-      <c r="B13" t="s">
-        <v>38</v>
-      </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" t="s">
         <v>41</v>
       </c>
-      <c r="B16" t="s">
-        <v>42</v>
-      </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:3" collapsed="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" t="s">
         <v>45</v>
       </c>
-      <c r="B21" t="s">
-        <v>46</v>
-      </c>
       <c r="C21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
         <v>23</v>
       </c>
-      <c r="B23" t="s">
-        <v>24</v>
-      </c>
       <c r="C23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" t="s">
         <v>27</v>
       </c>
-      <c r="B29" t="s">
-        <v>28</v>
-      </c>
       <c r="C29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
-        <v>32</v>
-      </c>
       <c r="C32" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C35" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" t="s">
         <v>37</v>
       </c>
-      <c r="B36" t="s">
-        <v>38</v>
-      </c>
       <c r="C36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C37" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C38" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C39" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C40" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" t="s">
         <v>45</v>
       </c>
-      <c r="B41" t="s">
-        <v>46</v>
-      </c>
       <c r="C41" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C42" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
+        <v>40</v>
+      </c>
+      <c r="B43" t="s">
         <v>41</v>
       </c>
-      <c r="B43" t="s">
-        <v>42</v>
-      </c>
       <c r="C43" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C44" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C45" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
+        <v>22</v>
+      </c>
+      <c r="B46" t="s">
         <v>23</v>
       </c>
-      <c r="B46" t="s">
-        <v>24</v>
-      </c>
       <c r="C46" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B47" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C47" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B48" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C48" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B49" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C49" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
+        <v>26</v>
+      </c>
+      <c r="B50" t="s">
         <v>27</v>
       </c>
-      <c r="B50" t="s">
-        <v>28</v>
-      </c>
       <c r="C50" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B51" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C51" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B52" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C52" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
+        <v>30</v>
+      </c>
+      <c r="B53" t="s">
         <v>31</v>
       </c>
-      <c r="B53" t="s">
-        <v>32</v>
-      </c>
       <c r="C53" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B54" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C54" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B55" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C55" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
+        <v>36</v>
+      </c>
+      <c r="B56" t="s">
         <v>37</v>
       </c>
-      <c r="B56" t="s">
-        <v>38</v>
-      </c>
       <c r="C56" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B57" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C57" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C58" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B59" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C59" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
+        <v>44</v>
+      </c>
+      <c r="B60" t="s">
         <v>45</v>
       </c>
-      <c r="B60" t="s">
-        <v>46</v>
-      </c>
       <c r="C60" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
+        <v>40</v>
+      </c>
+      <c r="B61" t="s">
         <v>41</v>
       </c>
-      <c r="B61" t="s">
-        <v>42</v>
-      </c>
       <c r="C61" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B62" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B63" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C63" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B64" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C64" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B65" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C65" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
+        <v>30</v>
+      </c>
+      <c r="B66" t="s">
         <v>31</v>
       </c>
-      <c r="B66" t="s">
-        <v>32</v>
-      </c>
       <c r="C66" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B67" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C67" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B68" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C68" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
+        <v>44</v>
+      </c>
+      <c r="B69" t="s">
         <v>45</v>
       </c>
-      <c r="B69" t="s">
-        <v>46</v>
-      </c>
       <c r="C69" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B70" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C70" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
+        <v>22</v>
+      </c>
+      <c r="B71" t="s">
         <v>23</v>
       </c>
-      <c r="B71" t="s">
-        <v>24</v>
-      </c>
       <c r="C71" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B72" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C72" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B73" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C73" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B74" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C74" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B75" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C75" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B76" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C76" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B77" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C77" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
+        <v>26</v>
+      </c>
+      <c r="B78" t="s">
         <v>27</v>
       </c>
-      <c r="B78" t="s">
-        <v>28</v>
-      </c>
       <c r="C78" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B79" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C79" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B80" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C80" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
+        <v>30</v>
+      </c>
+      <c r="B81" t="s">
         <v>31</v>
       </c>
-      <c r="B81" t="s">
-        <v>32</v>
-      </c>
       <c r="C81" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B82" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C82" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B83" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C83" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B84" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C84" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B85" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C85" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B86" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C86" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
+        <v>36</v>
+      </c>
+      <c r="B87" t="s">
         <v>37</v>
       </c>
-      <c r="B87" t="s">
-        <v>38</v>
-      </c>
       <c r="C87" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B88" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C88" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B89" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C89" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B90" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C90" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
+        <v>44</v>
+      </c>
+      <c r="B91" t="s">
         <v>45</v>
       </c>
-      <c r="B91" t="s">
-        <v>46</v>
-      </c>
       <c r="C91" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B92" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C92" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B93" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C93" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B94" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C94" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B95" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C95" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
+        <v>22</v>
+      </c>
+      <c r="B96" t="s">
         <v>23</v>
       </c>
-      <c r="B96" t="s">
-        <v>24</v>
-      </c>
       <c r="C96" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B97" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C97" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B98" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C98" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B99" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C99" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
+        <v>26</v>
+      </c>
+      <c r="B100" t="s">
         <v>27</v>
       </c>
-      <c r="B100" t="s">
-        <v>28</v>
-      </c>
       <c r="C100" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B101" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C101" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
+        <v>30</v>
+      </c>
+      <c r="B102" t="s">
         <v>31</v>
       </c>
-      <c r="B102" t="s">
-        <v>32</v>
-      </c>
       <c r="C102" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B103" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C103" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B104" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C104" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B105" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C105" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B106" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C106" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B107" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C107" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B108" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C108" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B109" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C109" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
+        <v>36</v>
+      </c>
+      <c r="B110" t="s">
         <v>37</v>
       </c>
-      <c r="B110" t="s">
-        <v>38</v>
-      </c>
       <c r="C110" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B111" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C111" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B112" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C112" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
+        <v>44</v>
+      </c>
+      <c r="B113" t="s">
         <v>45</v>
       </c>
-      <c r="B113" t="s">
-        <v>46</v>
-      </c>
       <c r="C113" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B114" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C114" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
+        <v>40</v>
+      </c>
+      <c r="B115" t="s">
         <v>41</v>
       </c>
-      <c r="B115" t="s">
-        <v>42</v>
-      </c>
       <c r="C115" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B116" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C116" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B117" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C117" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B118" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C118" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B119" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C119" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B120" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C120" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B121" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C121" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B122" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C122" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B123" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C123" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
+        <v>44</v>
+      </c>
+      <c r="B124" t="s">
         <v>45</v>
       </c>
-      <c r="B124" t="s">
-        <v>46</v>
-      </c>
       <c r="C124" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B125" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C125" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B126" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C126" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
+        <v>22</v>
+      </c>
+      <c r="B127" t="s">
         <v>23</v>
       </c>
-      <c r="B127" t="s">
-        <v>24</v>
-      </c>
       <c r="C127" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B128" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C128" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B129" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C129" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
+        <v>26</v>
+      </c>
+      <c r="B130" t="s">
         <v>27</v>
       </c>
-      <c r="B130" t="s">
-        <v>28</v>
-      </c>
       <c r="C130" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B131" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C131" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
+        <v>30</v>
+      </c>
+      <c r="B132" t="s">
         <v>31</v>
       </c>
-      <c r="B132" t="s">
-        <v>32</v>
-      </c>
       <c r="C132" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B133" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C133" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B134" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C134" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B135" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C135" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
+        <v>36</v>
+      </c>
+      <c r="B136" t="s">
         <v>37</v>
       </c>
-      <c r="B136" t="s">
-        <v>38</v>
-      </c>
       <c r="C136" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B137" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C137" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B138" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C138" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
+        <v>44</v>
+      </c>
+      <c r="B139" t="s">
         <v>45</v>
       </c>
-      <c r="B139" t="s">
-        <v>46</v>
-      </c>
       <c r="C139" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B140" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C140" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B141" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C141" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B142" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C142" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B143" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C143" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -2439,109 +2429,109 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" t="s">
         <v>67</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>68</v>
-      </c>
-      <c r="C1" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" t="s">
         <v>70</v>
-      </c>
-      <c r="C2" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" t="s">
         <v>73</v>
-      </c>
-      <c r="C4" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" t="s">
         <v>80</v>
-      </c>
-      <c r="B10" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/niclasl/src/hockey/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{477B0544-71F0-5E4E-A657-DD1781C004EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B8A5CD8-AC79-DD45-97A8-5159B3686E98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38720" yWindow="-1640" windowWidth="26240" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="520" windowWidth="26240" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Innstillinger" sheetId="1" r:id="rId1"/>
@@ -34,9 +34,6 @@
     <t>start_date</t>
   </si>
   <si>
-    <t>2026-10-01</t>
-  </si>
-  <si>
     <t>end_date</t>
   </si>
   <si>
@@ -266,6 +263,9 @@
   </si>
   <si>
     <t>fixed_allocation</t>
+  </si>
+  <si>
+    <t>2026-10-09</t>
   </si>
 </sst>
 </file>
@@ -626,15 +626,15 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
         <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -654,24 +654,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>7</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>9</v>
-      </c>
-      <c r="E1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>4</v>
@@ -688,7 +688,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3">
         <v>4</v>
@@ -705,7 +705,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4">
         <v>4</v>
@@ -722,7 +722,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -739,7 +739,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>3</v>
@@ -756,7 +756,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7">
         <v>3</v>
@@ -773,7 +773,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8">
         <v>3</v>
@@ -790,7 +790,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -807,7 +807,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10">
         <v>2</v>
@@ -816,10 +816,10 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -841,1575 +841,1575 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" t="s">
-        <v>21</v>
-      </c>
       <c r="C1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
         <v>22</v>
       </c>
-      <c r="B2" t="s">
-        <v>23</v>
-      </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
         <v>26</v>
       </c>
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
         <v>30</v>
       </c>
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" t="s">
         <v>36</v>
       </c>
-      <c r="B13" t="s">
-        <v>37</v>
-      </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" t="s">
         <v>40</v>
       </c>
-      <c r="B16" t="s">
-        <v>41</v>
-      </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:3" collapsed="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" t="s">
         <v>44</v>
       </c>
-      <c r="B21" t="s">
-        <v>45</v>
-      </c>
       <c r="C21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
-        <v>23</v>
-      </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
         <v>26</v>
       </c>
-      <c r="B29" t="s">
-        <v>27</v>
-      </c>
       <c r="C29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32" t="s">
         <v>30</v>
       </c>
-      <c r="B32" t="s">
-        <v>31</v>
-      </c>
       <c r="C32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
         <v>36</v>
       </c>
-      <c r="B36" t="s">
-        <v>37</v>
-      </c>
       <c r="C36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C37" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C38" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C39" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C40" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" t="s">
         <v>44</v>
       </c>
-      <c r="B41" t="s">
-        <v>45</v>
-      </c>
       <c r="C41" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
+        <v>39</v>
+      </c>
+      <c r="B43" t="s">
         <v>40</v>
       </c>
-      <c r="B43" t="s">
-        <v>41</v>
-      </c>
       <c r="C43" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C44" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C45" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
+        <v>21</v>
+      </c>
+      <c r="B46" t="s">
         <v>22</v>
       </c>
-      <c r="B46" t="s">
-        <v>23</v>
-      </c>
       <c r="C46" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B47" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C47" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C48" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C49" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
+        <v>25</v>
+      </c>
+      <c r="B50" t="s">
         <v>26</v>
       </c>
-      <c r="B50" t="s">
-        <v>27</v>
-      </c>
       <c r="C50" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B51" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C51" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B52" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C52" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
+        <v>29</v>
+      </c>
+      <c r="B53" t="s">
         <v>30</v>
       </c>
-      <c r="B53" t="s">
-        <v>31</v>
-      </c>
       <c r="C53" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B54" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C54" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B55" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C55" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
+        <v>35</v>
+      </c>
+      <c r="B56" t="s">
         <v>36</v>
       </c>
-      <c r="B56" t="s">
-        <v>37</v>
-      </c>
       <c r="C56" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B57" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C57" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B58" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C58" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B59" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C59" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
+        <v>43</v>
+      </c>
+      <c r="B60" t="s">
         <v>44</v>
       </c>
-      <c r="B60" t="s">
-        <v>45</v>
-      </c>
       <c r="C60" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
+        <v>39</v>
+      </c>
+      <c r="B61" t="s">
         <v>40</v>
       </c>
-      <c r="B61" t="s">
-        <v>41</v>
-      </c>
       <c r="C61" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B62" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C62" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B63" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C63" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B64" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C64" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B65" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C65" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
+        <v>29</v>
+      </c>
+      <c r="B66" t="s">
         <v>30</v>
       </c>
-      <c r="B66" t="s">
-        <v>31</v>
-      </c>
       <c r="C66" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B67" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C67" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B68" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C68" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
+        <v>43</v>
+      </c>
+      <c r="B69" t="s">
         <v>44</v>
       </c>
-      <c r="B69" t="s">
-        <v>45</v>
-      </c>
       <c r="C69" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B70" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C70" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
+        <v>21</v>
+      </c>
+      <c r="B71" t="s">
         <v>22</v>
       </c>
-      <c r="B71" t="s">
-        <v>23</v>
-      </c>
       <c r="C71" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B72" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C72" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B73" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C73" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B74" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C74" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B75" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C75" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B76" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C76" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B77" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C77" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
+        <v>25</v>
+      </c>
+      <c r="B78" t="s">
         <v>26</v>
       </c>
-      <c r="B78" t="s">
-        <v>27</v>
-      </c>
       <c r="C78" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B79" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C79" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B80" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C80" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
+        <v>29</v>
+      </c>
+      <c r="B81" t="s">
         <v>30</v>
       </c>
-      <c r="B81" t="s">
-        <v>31</v>
-      </c>
       <c r="C81" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B82" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C82" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B83" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C83" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B84" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C84" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B85" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C85" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B86" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C86" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
+        <v>35</v>
+      </c>
+      <c r="B87" t="s">
         <v>36</v>
       </c>
-      <c r="B87" t="s">
-        <v>37</v>
-      </c>
       <c r="C87" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B88" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C88" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B89" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C89" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B90" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C90" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
+        <v>43</v>
+      </c>
+      <c r="B91" t="s">
         <v>44</v>
       </c>
-      <c r="B91" t="s">
-        <v>45</v>
-      </c>
       <c r="C91" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B92" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C92" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B93" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C93" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B94" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C94" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B95" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C95" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
+        <v>21</v>
+      </c>
+      <c r="B96" t="s">
         <v>22</v>
       </c>
-      <c r="B96" t="s">
-        <v>23</v>
-      </c>
       <c r="C96" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B97" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C97" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B98" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C98" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B99" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C99" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
+        <v>25</v>
+      </c>
+      <c r="B100" t="s">
         <v>26</v>
       </c>
-      <c r="B100" t="s">
-        <v>27</v>
-      </c>
       <c r="C100" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B101" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C101" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
+        <v>29</v>
+      </c>
+      <c r="B102" t="s">
         <v>30</v>
       </c>
-      <c r="B102" t="s">
-        <v>31</v>
-      </c>
       <c r="C102" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B103" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C103" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B104" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C104" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B105" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C105" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B106" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C106" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B107" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C107" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B108" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C108" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B109" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C109" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
+        <v>35</v>
+      </c>
+      <c r="B110" t="s">
         <v>36</v>
       </c>
-      <c r="B110" t="s">
-        <v>37</v>
-      </c>
       <c r="C110" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B111" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C111" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B112" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C112" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
+        <v>43</v>
+      </c>
+      <c r="B113" t="s">
         <v>44</v>
       </c>
-      <c r="B113" t="s">
-        <v>45</v>
-      </c>
       <c r="C113" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B114" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C114" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
+        <v>39</v>
+      </c>
+      <c r="B115" t="s">
         <v>40</v>
       </c>
-      <c r="B115" t="s">
-        <v>41</v>
-      </c>
       <c r="C115" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B116" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C116" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B117" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C117" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B118" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C118" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B119" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C119" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B120" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C120" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B121" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C121" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B122" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C122" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B123" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C123" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
+        <v>43</v>
+      </c>
+      <c r="B124" t="s">
         <v>44</v>
       </c>
-      <c r="B124" t="s">
-        <v>45</v>
-      </c>
       <c r="C124" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B125" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C125" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B126" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C126" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
+        <v>21</v>
+      </c>
+      <c r="B127" t="s">
         <v>22</v>
       </c>
-      <c r="B127" t="s">
-        <v>23</v>
-      </c>
       <c r="C127" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B128" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C128" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B129" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C129" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
+        <v>25</v>
+      </c>
+      <c r="B130" t="s">
         <v>26</v>
       </c>
-      <c r="B130" t="s">
-        <v>27</v>
-      </c>
       <c r="C130" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B131" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C131" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
+        <v>29</v>
+      </c>
+      <c r="B132" t="s">
         <v>30</v>
       </c>
-      <c r="B132" t="s">
-        <v>31</v>
-      </c>
       <c r="C132" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B133" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C133" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B134" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C134" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B135" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C135" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
+        <v>35</v>
+      </c>
+      <c r="B136" t="s">
         <v>36</v>
       </c>
-      <c r="B136" t="s">
-        <v>37</v>
-      </c>
       <c r="C136" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B137" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C137" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B138" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C138" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
+        <v>43</v>
+      </c>
+      <c r="B139" t="s">
         <v>44</v>
       </c>
-      <c r="B139" t="s">
-        <v>45</v>
-      </c>
       <c r="C139" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B140" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C140" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B141" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C141" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B142" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C142" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B143" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C143" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -2429,109 +2429,109 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" t="s">
         <v>66</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>67</v>
-      </c>
-      <c r="C1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" t="s">
         <v>69</v>
-      </c>
-      <c r="C2" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" t="s">
         <v>72</v>
-      </c>
-      <c r="C4" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" t="s">
         <v>79</v>
-      </c>
-      <c r="B10" t="s">
-        <v>80</v>
       </c>
     </row>
   </sheetData>
